--- a/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
+++ b/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
@@ -10,13 +10,15 @@
     <sheet name="0. Lee me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. Taxonomias" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Ejes transversales" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Desglose capacidades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Columna C propuesta" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Matriz propuesta" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6. Hallazgos y decisiones" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3. Meta-capacidades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Etica del liderazgo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Desglose capacidades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Columna C propuesta" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. Matriz propuesta" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8. Hallazgos y decisiones" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Desglose capacidades'!$A$4:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5. Desglose capacidades'!$A$4:$F$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +67,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -180,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -222,6 +230,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -234,7 +255,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -669,15 +689,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="141" customHeight="1">
+    <row r="13" ht="201" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>1. Taxonomías — el diccionario: nueve clases (T1 a T9), tres ejes transversales (E1 a E3) y dos categorías de control (X, Y) para lo que hoy está en la columna sin ser una capacidad.
+          <t>1. Taxonomías — el diccionario: la meta-capacidad (T0), nueve clases (T1 a T9), tres ejes transversales (E1 a E3) y dos categorías de control (X, Y) para lo que hoy está en la columna sin ser una capacidad.
 2. Ejes transversales — campos de investigación (incluye la respuesta a «¿alguna más?»), sujetos y especialidad de diseño.
-3. Desglose capacidades — los ítems actuales, uno por fila, con su clase, su nombre normalizado y la decisión propuesta.
-4. Columna C propuesta — la columna reescrita y ordenada por niveles, lista para pegar.
-5. Matriz propuesta — la matriz completa con la columna C nueva y el resto intacto.
-6. Hallazgos y decisiones — los problemas detectados y las preguntas abiertas para cerrar con los dos leads.</t>
+3. Meta-capacidades — una por dimensión: qué compone, qué pregunta resuelve, cómo progresa de Professional a Master y cómo cambia según el campo.
+4. Ética del liderazgo — el modelo de medición de T7b: el equilibrio que se pondera, el umbral que se verifica, los indicadores, la aplicación por nivel y las cautelas del instrumento.
+5. Desglose capacidades — los ítems actuales, uno por fila, con su clase, su nombre normalizado y la decisión propuesta.
+6. Columna C propuesta — la columna reescrita y ordenada por niveles, lista para pegar.
+7. Matriz propuesta — la matriz completa con la columna C nueva y el resto intacto.
+8. Hallazgos y decisiones — los problemas detectados y las preguntas abiertas para cerrar con los dos leads.</t>
         </is>
       </c>
     </row>
@@ -688,10 +710,25 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>META-CAPACIDAD (si aplica) → T1 Objetivo → T2 Enfoque → T3 Metodología → T4 Técnica → T5 Marco conceptual → T6 Artefacto → T7 Calidad y ética → T8 Práctica operativa → T9 Competencia transversal.</t>
+          <t>T0 Meta-capacidad → T1 Objetivo → T2 Enfoque → T3 Metodología → T4 Técnica → T5 Marco conceptual → T6 Artefacto → T7 Calidad y ética (T7b Ética del liderazgo donde corresponde) → T8 Práctica operativa → T9 Competencia transversal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Dos incorporaciones sobre la primera versión</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="111" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>(a) META-CAPACIDAD EN TODAS LAS DIMENSIONES. Antes existía solo en D1 y sin nombrarse como tal. Ahora cada dimensión declara la suya: es lo que distingue elegir bien de ejecutar mucho, y es donde debe anclarse la progresión Specialist→Expert.
+(b) ÉTICA DEL LIDERAZGO (T7b). Donde hay liderazgo, la ética se mide como el equilibrio entre la productividad del equipo y su satisfacción con quien lidera. El respeto básico —sin acoso, sin mansplaining, sin conductas excluyentes— NO forma parte de ese equilibrio: es un umbral que se verifica y que bloquea el nivel. Ponerlo en la balanza equivaldría a decir que un buen resultado puede compensarlo.</t>
         </is>
       </c>
     </row>
@@ -706,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -852,7 +889,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NIVELES DE LA CAPACIDAD — de más abstracto (T1) a más concreto (T4); T5 a T9 son transversales</t>
+          <t>NIVELES DE LA CAPACIDAD — T0 gobierna la composición; T1 a T4 son secuencia; T5 a T9, transversales</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -863,306 +900,333 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>T1. Objetivo</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>¿Para qué investigamos o intervenimos?</t>
+          <t>¿Sabe elegir, no solo ejecutar?</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>La intención de conocimiento o de cambio. Define el tipo de pregunta, no el modo de responderla. Es el nivel más alto: primero se decide el objetivo, después todo lo demás.</t>
+          <t>La capacidad de COMPONER los niveles T1–T4 de forma coherente con la decisión que hay que tomar: elegir el objetivo correcto, el enfoque proporcionado, la metodología que la decisión exige y la técnica que corresponde. Es lo que distingue a un Specialist de un Expert: no ejecutar mejor, elegir mejor. Cada dimensión tiene la suya.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Diagnóstico conductual · Diagnóstico sistémico · Exploración / discovery · Validación (UX validation) · Evaluación de impacto · Problem framing · Opportunity framing</t>
+          <t>D1 Estrategia de investigación · D2 Juicio estratégico · D3 Criterio de intervención · D4 Criterio de evidencia · D5 Criterio de escalamiento y liderazgo</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Encabeza la columna «Capacidades incluidas» de cada dimensión.</t>
+          <t>Encabeza cada dimensión, por encima de T1. Ver hoja «3. Meta-capacidades».</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>T2. Enfoque</t>
+          <t>T1. Objetivo</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>¿Con qué lógica de evidencia?</t>
+          <t>¿Para qué investigamos o intervenimos?</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>El paradigma que gobierna la evidencia. Tres cortes independientes: naturaleza del dato (cuali / cuanti / mixto), origen (primaria / secundaria) y control (observacional / experimental).</t>
+          <t>La intención de conocimiento o de cambio. Define el tipo de pregunta, no el modo de responderla. Es el nivel más alto: primero se decide el objetivo, después todo lo demás.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Cualitativo · Cuantitativo · Mixto · Primario / secundario · Observacional / experimental</t>
+          <t>Diagnóstico conductual · Diagnóstico sistémico · Exploración / discovery · Validación (UX validation) · Evaluación de impacto · Problem framing · Opportunity framing</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Segundo bloque de la columna.</t>
+          <t>Encabeza la columna «Capacidades incluidas» de cada dimensión.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>T3. Metodología</t>
+          <t>T2. Enfoque</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>¿Cómo se estructura el estudio?</t>
+          <t>¿Con qué lógica de evidencia?</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>El diseño global de la investigación: qué se compara, con quién, en cuántos momentos y bajo qué control. Una metodología admite varias técnicas.</t>
+          <t>El paradigma que gobierna la evidencia. Tres cortes independientes: naturaleza del dato (cuali / cuanti / mixto), origen (primaria / secundaria) y control (observacional / experimental).</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Desk research · Etnografía / investigación en campo · Estudio longitudinal · Diseño experimental · RCT · Cuasi-experimento · Pre-post con control · Encuesta poblacional</t>
+          <t>Cualitativo · Cuantitativo · Mixto · Primario / secundario · Observacional / experimental</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Tercer bloque de la columna.</t>
+          <t>Segundo bloque de la columna.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>T4. Técnica / instrumento</t>
+          <t>T3. Metodología</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>¿Con qué herramienta concreta se recoge o se analiza?</t>
+          <t>¿Cómo se estructura el estudio?</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>El instrumento operativo. Se subdivide en técnicas de recolección y técnicas de análisis. Una misma técnica sirve a metodologías distintas: por eso no puede ir al mismo nivel que la metodología.</t>
+          <t>El diseño global de la investigación: qué se compara, con quién, en cuántos momentos y bajo qué control. Una metodología admite varias técnicas.</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Recolección: entrevista · observación estructurada · diario · encuesta · intercept · mystery shopping · usability test · concept &amp; prototype testing · A/B test · analytics.   Análisis: diseño muestral · codificación · triangulación · síntesis · análisis estadístico</t>
+          <t>Desk research · Etnografía / investigación en campo · Estudio longitudinal · Diseño experimental · RCT · Cuasi-experimento · Pre-post con control · Encuesta poblacional</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Cuarto bloque de la columna.</t>
+          <t>Tercer bloque de la columna.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>T5. Marco conceptual</t>
+          <t>T4. Técnica / instrumento</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>¿Con qué lente interpretamos?</t>
+          <t>¿Con qué herramienta concreta se recoge o se analiza?</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Modelos y teorías que ordenan la lectura del comportamiento y del sistema. No son métodos: no dicen cómo recoger datos, dicen cómo leerlos.</t>
+          <t>El instrumento operativo. Se subdivide en técnicas de recolección y técnicas de análisis. Una misma técnica sirve a metodologías distintas: por eso no puede ir al mismo nivel que la metodología.</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Frameworks de ciencias del comportamiento (COM-B, EAST, MINDSPACE) · Systems thinking · Journey thinking · Arquitectura de decisiones · Inferencia causal · Teoría del cambio</t>
+          <t>Recolección: entrevista · observación estructurada · diario · encuesta · intercept · mystery shopping · usability test · concept &amp; prototype testing · A/B test · analytics.   Análisis: diseño muestral · codificación · triangulación · síntesis · análisis estadístico</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Bloque transversal dentro de la columna.</t>
+          <t>Cuarto bloque de la columna.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>T6. Artefacto / output</t>
+          <t>T5. Marco conceptual</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>¿Qué produce la capacidad?</t>
+          <t>¿Con qué lente interpretamos?</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>El entregable observable. Es lo que permite evidenciar el nivel en la evaluación; hoy está mezclado con los métodos que lo producen.</t>
+          <t>Modelos y teorías que ordenan la lectura del comportamiento y del sistema. No son métodos: no dicen cómo recoger datos, dicen cómo leerlos.</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Insight · Hipótesis priorizada · Principios y criterios de diseño · Métricas y criterios de éxito · Concepto de intervención · Prototipo conceptual · Repositorio de evidencia</t>
+          <t>Frameworks de ciencias del comportamiento (COM-B, EAST, MINDSPACE) · Systems thinking · Journey thinking · Arquitectura de decisiones · Inferencia causal · Teoría del cambio</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Bloque transversal; conecta directo con la columna «Evidencias sugeridas».</t>
+          <t>Bloque transversal dentro de la columna.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>T7. Calidad y ética</t>
+          <t>T6. Artefacto / output</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>¿Bajo qué estándar es válido?</t>
+          <t>¿Qué produce la capacidad?</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Criterios que hacen la evidencia y la intervención defendibles. Deben aparecer en las cinco dimensiones, no solo en una.</t>
+          <t>El entregable observable. Es lo que permite evidenciar el nivel en la evaluación; hoy está mezclado con los métodos que lo producen.</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Calidad y suficiencia de evidencia · Gestión de sesgos · Validez interna y externa · Control de variables · Potencia y tamaño muestral · Ética de la investigación y de la influencia · Privacidad y trazabilidad</t>
+          <t>Insight · Hipótesis priorizada · Principios y criterios de diseño · Métricas y criterios de éxito · Concepto de intervención · Prototipo conceptual · Repositorio de evidencia</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Bloque transversal en las 5 dimensiones.</t>
+          <t>Bloque transversal; conecta directo con la columna «Evidencias sugeridas».</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>T8. Práctica operativa (Ops)</t>
+          <t>T7. Calidad y ética</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>¿Cómo se sostiene y escala en el tiempo?</t>
+          <t>¿Bajo qué estándar es válido?</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Sistemas, procesos y activos que convierten estudios sueltos en capacidad organizacional acumulativa.</t>
+          <t>Criterios que hacen la evidencia, la intervención y el ejercicio del liderazgo defendibles. Deben aparecer en las cinco dimensiones, no solo en una. Donde hay liderazgo, la ética deja de ser solo ética de la evidencia y pasa a ser también ética del trato con el equipo.</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>ResearchOps · BehavioralOps · KnowledgeOps · Gobernanza y estándares · Capability building · Mejora continua · Automatización</t>
+          <t>Calidad y suficiencia de evidencia · Gestión de sesgos · Validez interna y externa · Control de variables · Potencia y tamaño muestral · Ética de la investigación y de la influencia · Privacidad y trazabilidad · Ética del liderazgo (ver hoja «4. Ética del liderazgo»)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Concentrado en la Dimensión 5.</t>
+          <t>Bloque transversal en las 5 dimensiones. En D5 y en los niveles 3–4 de todas las dimensiones incluye la ética del liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>T8. Práctica operativa (Ops)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>¿Cómo se sostiene y escala en el tiempo?</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Sistemas, procesos y activos que convierten estudios sueltos en capacidad organizacional acumulativa.</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ResearchOps · BehavioralOps · KnowledgeOps · Gobernanza y estándares · Capability building · Mejora continua · Automatización</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Concentrado en la Dimensión 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
           <t>T9. Competencia transversal</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>¿Qué habilidad profesional lo hace posible?</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Habilidades no metodológicas que atraviesan todas las dimensiones. No son research ni diseño: son el vehículo. Conviene declararlas aparte para no inflar las dimensiones técnicas.</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Pensamiento crítico · Business acumen · Storytelling estratégico · Facilitación · Influencia · Stakeholder management · Mentoring · Priorización · Comunicación estratégica</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Bloque de cierre en cada dimensión, o columna propia.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>CATEGORÍAS DE CONTROL — lo que NO es capacidad y hoy está dentro de la columna</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>X. Modelo de colaboración</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>¿Con quién se trabaja y en qué rol?</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Describe el alcance de la relación con otros equipos (PD/SD, Data, Negocio). No es una habilidad evaluable: su progresión ya está descrita en los niveles 1 a 4.</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Acompañamiento a Product / Service Design · Trabajo con Data &amp; Analytics · Interlocución con negocio</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Sacar de «Capacidades incluidas» → describir en la definición del rol y en los niveles.</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>X. Modelo de colaboración</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>¿Con quién se trabaja y en qué rol?</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Describe el alcance de la relación con otros equipos (PD/SD, Data, Negocio). No es una habilidad evaluable: su progresión ya está descrita en los niveles 1 a 4.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Acompañamiento a Product / Service Design · Trabajo con Data &amp; Analytics · Interlocución con negocio</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Sacar de «Capacidades incluidas» → describir en la definición del rol y en los niveles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>Y. Resultado organizacional</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>¿Qué efecto buscamos en la organización?</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Estados deseados de la organización, no capacidades de una persona. Evaluarlos como capacidad individual genera ambigüedad.</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Cultura de evidencia · Continuous learning · Reconocimiento de la capacidad</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Sacar de «Capacidades incluidas» → propósito de la dimensión.</t>
         </is>
@@ -1523,7 +1587,809 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>T0 — Una meta-capacidad por dimensión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>La meta-capacidad no es una capacidad más: es la que gobierna cómo se componen las demás. Responde a «¿sabe elegir, no solo ejecutar?» y es donde debe anclarse la progresión Specialist→Expert. Antes existía solo en D1, y sin nombrarse como tal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Meta-capacidad</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Qué compone</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>La pregunta que resuelve</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Cómo progresa (1 → 4)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cómo se evidencia</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cómo cambia según el campo (E1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="118" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1. Discovery e Insights</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Estrategia de investigación</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>T1 objetivo + T2 enfoque + T3 metodología + T4 técnica</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>¿Es esta la investigación que esta decisión necesita, o solo la que sabemos hacer?</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>1 Professional: ejecuta la estrategia que otro definió y reconoce sus límites.  2 Specialist: elige metodología y técnicas para un objetivo dado.  3 Expert: define el objetivo y combina métodos para problemas ambiguos o mal formulados.  4 Master: define qué preguntas merece hacerse la organización antes de que alguien las pida.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Plan de investigación con la justificación del método frente a alternativas descartadas, y no solo el método elegido.</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>En Digital el sesgo es sobrerrepresentar lo instrumentable; en Físico, el acceso al campo condiciona el diseño; en Híbrido, la unidad de análisis es la transición entre canales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2. Estrategia y Problem Solving</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Juicio estratégico</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>T1 framing + T5 marco + T7 criterio de suficiencia + T9 lectura de negocio</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>¿Qué problema merece resolverse, y con cuánta evidencia basta para decidirlo?</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>1 Professional: interpreta insights dentro de un encuadre dado.  2 Specialist: reencuadra el problema e integra usuario, conducta y negocio.  3 Expert: sostiene la decisión bajo evidencia incompleta y hace explícito el riesgo de equivocarse.  4 Master: cambia el encuadre con el que la organización lee sus propios problemas.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Una decisión tomada con evidencia parcial, con el umbral de suficiencia declarado por adelantado y revisado después.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>El campo condiciona el costo de equivocarse: en Físico la corrección es lenta y cara, lo que sube el estándar de evidencia exigible antes de decidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="118" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>3. Diseño y Orquestación de Experiencias</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Criterio de intervención</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>T1 conducta objetivo + T5 palanca + T7 ética de la influencia</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>¿Cuánta intervención pide esta conducta — y cuándo lo correcto es no intervenir?</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>1 Professional: aplica palancas conocidas a problemas acotados.  2 Specialist: elige la palanca proporcional al problema y la justifica.  3 Expert: orquesta intervenciones múltiples anticipando efectos de segundo orden.  4 Master: define qué está y qué no está permitido intervenir, y por qué.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Una intervención descartada por desproporcionada o por riesgo ético, con el razonamiento escrito. Saber no intervenir es evidencia de nivel, no ausencia de trabajo.</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>En Físico la intervención es más difícil de revertir y afecta a terceros presentes; en Híbrido el riesgo es que la palanca funcione en un canal y rompa el otro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="118" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4. Experimentación, Medición e Impacto</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Criterio de evidencia</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>T1 objetivo evaluativo + T2 control + T3 metodología + T7 validez</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>¿Cuánto rigor exige esta decisión — y cuánto sería desperdiciarlo?</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>1 Professional: ejecuta la validación definida y lee sus límites.  2 Specialist: elige el diseño según la evidencia que la decisión necesita.  3 Expert: ajusta rigor, costo, reversibilidad y riesgo, y defiende la causalidad que afirma.  4 Master: define el estándar de evidencia por tipo de decisión para toda la organización.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Dos decisiones resueltas con distinto nivel de rigor y la justificación de por qué cada una merecía el suyo.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>En Digital el experimento es barato y reversible; en Físico rara vez hay aleatorización posible, y el cuasi-experimento por sede pasa a ser el diseño de referencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="118" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Criterio de escalamiento y liderazgo</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>T8 práctica operativa + T7 gobernanza y ética del liderazgo + T9 influencia</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>¿Qué se estandariza, qué se deja variar, y a qué ritmo se le puede exigir a un equipo?</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>1 Professional: usa los procesos y documenta para otros.  2 Specialist: mejora prácticas y acompaña a personas.  3 Expert: decide qué se vuelve estándar y sostiene el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.  4 Master: responde por que ese equilibrio esté instrumentado y auditado, no solo declarado.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Un estándar adoptado sin imposición, y el resultado del feedback ascendente del equipo junto a su indicador de entrega en el mismo periodo.</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Transversal a los campos. Lo que cambia con el campo es el costo operativo de cada estándar, no el criterio.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>T7b — Ética del liderazgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Aplica en la Dimensión 5 y como condición de los niveles 3 y 4 de todas las dimensiones, que es donde la matriz ya describe liderar, orientar y desarrollar personas. Se mide en dos partes que NO se mezclan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Parte</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Qué es</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cómo se trata</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Por qué así</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>A. El equilibrio</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Productividad del equipo ↔ satisfacción del equipo con la persona que lidera.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Se mide y se pondera. Ninguno de los dos se lee solo.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Un líder con alta entrega y baja satisfacción está quemando al equipo y la matriz debe verlo. Un líder muy valorado con el equipo estancado tampoco está en nivel. El nivel está en sostener ambos a la vez, no en maximizar uno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>B. El umbral</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Respeto básico: sin acoso, sin mansplaining, sin conductas excluyentes en el trato cotidiano.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Se verifica, NO se pondera. Es un piso, no una variable.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Si el respeto básico entrara en la balanza, la matriz estaría diciendo que un buen resultado puede compensarlo. No puede. El incumplimiento verificado bloquea el nivel, por alto que sea el equilibrio de la parte A y por alto que sea el puntaje en las otras cuatro dimensiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Indicadores sugeridos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>A · Productividad del equipo</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Estudios e intervenciones entregados Y usados en una decisión</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>ResearchOps / KnowledgeOps</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Entregado sin uso no cuenta: mide actividad, no valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>A · Productividad del equipo</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Tiempo de ciclo de la evidencia: de pregunta a decisión</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>ResearchOps</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Es el indicador que más tienta a forzar al equipo. Por eso nunca se lee sin el bloque de satisfacción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>A · Productividad del equipo</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Reutilización del conocimiento y cumplimiento del estándar metodológico</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>KnowledgeOps / gestión de calidad</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Distingue producir mucho de producir capacidad acumulativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>A · Satisfacción con quien lidera</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Feedback ascendente anónimo: claridad de dirección, apoyo al desarrollo, seguridad psicológica para discrepar</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Encuesta al equipo directo, anónima</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>n mínimo de 5 respuestas para publicar cualquier resultado. Por debajo, se reporta agregado o no se reporta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>A · Satisfacción con quien lidera</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Intención declarada de volver a trabajar con esa persona</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Encuesta al equipo directo, anónima</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Es el indicador que mejor resiste la deseabilidad social: pregunta por conducta futura, no por opinión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>A · Satisfacción con quien lidera</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Rotación voluntaria del equipo y motivo declarado en la salida</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Personas / entrevista de salida</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Indicador rezagado: confirma, no anticipa. Nunca se usa solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>B · Respeto básico (umbral)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Distribución del habla, de las interrupciones y de la atribución de ideas en reuniones</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Observación estructurada de sesiones reales</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Es la medición directa del mansplaining: quién es interrumpido y a quién se le atribuye después la idea. Es conducta observable, no percepción — y es exactamente la técnica que este equipo ya sabe aplicar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>B · Respeto básico (umbral)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Equidad en la asignación de oportunidades visibles: quién presenta al comité, quién lleva el estudio estratégico</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Registro de asignaciones del periodo</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>El trato desigual aparece antes en el reparto de oportunidades que en un reporte formal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>B · Respeto básico (umbral)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Atribución de autoría en entregables y presentaciones</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Repositorio de evidencia</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Trazable sin necesidad de encuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>B · Respeto básico (umbral)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Casos abiertos o sostenidos en el canal formal de reporte</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Canal de la organización</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Es la verificación final, no la primera señal. Una matriz que solo mira aquí llega tarde siempre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Cómo se aplica en cada nivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Equilibrio (se pondera)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Umbral (se verifica)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>1 — Professional</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>No lidera equipo: no hay equilibrio que medir.</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>El umbral aplica igual, a su conducta como integrante: respeto, escucha, atribución de ideas ajenas.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>2 — Specialist</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Lidera estudios y acompaña a otras personas. Primeras señales del equilibrio: satisfacción de quienes acompaña, junto al avance de lo que lidera.</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Umbral verificado con las personas a las que acompaña, no solo con su jefatura.</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="n"/>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>3 — Expert</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Lidera personas y prácticas. El equilibrio se mide formalmente: feedback ascendente anónimo y entrega del equipo, leídos en el mismo periodo y juntos.</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Umbral verificado con el equipo directo. Un incumplimiento verificado impide alcanzar o mantener este nivel.</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>4 — Master</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Define la gobernanza. Además de sostener su propio equilibrio, responde por que exista el sistema: los indicadores, el canal, el anonimato y la consecuencia.</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Umbral verificado y, además, instrumentado para toda la capacidad. Un Master no alcanza el nivel si el sistema de medición no existe, aunque su equipo esté satisfecho.</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Cautelas del instrumento — medir esto mal hace más daño que no medirlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Anonimato con n mínimo</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Por debajo de 5 respuestas no se publica resultado desagregado. Medir satisfacción con el líder en un equipo de tres personas sin protección es exponer a quien responde.</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Sin represalia, y verificable</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>El acceso al resultado desagregado y el momento de entrega deben estar definidos antes de la primera medición, no después de conocer el resultado.</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>La percepción de la jefatura no sustituye la del equipo</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>El umbral se verifica con las personas que reciben el trato, no con quien supervisa a quien lo da. Es el error de diseño más común de estos sistemas.</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>El equilibrio se lee en el mismo periodo</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Productividad de un trimestre contra satisfacción de otro permite justificar cualquier cosa. Misma ventana temporal o no se lee.</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>Umbral incumplido no se compensa</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>No entra en la ponderación 30/20/15/20/15. Bloquea el nivel con independencia del puntaje de las otras cuatro dimensiones.</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B34:D34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1625,7 +2491,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>META-CAPACIDAD</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1640,7 +2506,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Es la capacidad de ARTICULAR los niveles T1–T4. Ponerla como un ítem más de la lista la iguala a una técnica. Recomendación: declararla meta-capacidad de la dimensión.</t>
+          <t>Es la capacidad de ARTICULAR los niveles T1–T4. Ponerla como un ítem más de la lista la iguala a una técnica. Es la única meta-capacidad que la matriz ya tenía, aunque sin nombrarla como tal.</t>
         </is>
       </c>
     </row>
@@ -1657,7 +2523,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>META-CAPACIDAD</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -2013,7 +2879,7 @@
           <t>Etnografía y observación en campo; intercept; mystery shopping; shadowing</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Añadir (gap)</t>
         </is>
@@ -2359,32 +3225,32 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>3. Diseño y Orquestación de Experiencias</t>
+          <t>2. Estrategia y Problem Solving</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>diseño de intervenciones conductuales</t>
+          <t>— ausente —</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>T1. Objetivo + E3. Especialidad</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Diseño conductual: intervenir sobre una conducta objetivo</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Mantener — elevar</t>
+          <t>Juicio estratégico: qué problema merece resolverse y con cuánta evidencia basta para decidirlo</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Es el núcleo de la única especialidad de diseño de la matriz. Debe encabezar la dimensión, no aparecer como un ítem más de una enumeración.</t>
+          <t>La dimensión enumera técnicas de encuadre pero no la capacidad de elegir entre ellas. Sin meta-capacidad, la progresión Specialist→Expert se lee como «conoce más frameworks».</t>
         </is>
       </c>
     </row>
@@ -2396,25 +3262,29 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>arquitectura de decisiones</t>
+          <t>diseño de intervenciones conductuales</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>T5. Marco conceptual</t>
+          <t>T1. Objetivo + E3. Especialidad</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura de decisiones</t>
+          <t>Diseño conductual: intervenir sobre una conducta objetivo</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr"/>
+          <t>Mantener — elevar</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Es el núcleo de la única especialidad de diseño de la matriz. Debe encabezar la dimensión, no aparecer como un ítem más de una enumeración.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -2424,17 +3294,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>traducción de insights a diseño</t>
+          <t>arquitectura de decisiones</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica (proceso)</t>
+          <t>T5. Marco conceptual</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Traducción de insights y evidencia a criterios de diseño</t>
+          <t>Arquitectura de decisiones</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2452,22 +3322,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>principios y criterios de diseño</t>
+          <t>traducción de insights a diseño</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>T6. Artefacto / output</t>
+          <t>T4. Técnica (proceso)</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Principios y criterios de diseño</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
+          <t>Traducción de insights y evidencia a criterios de diseño</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
@@ -2480,22 +3350,22 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ideación y conceptualización</t>
+          <t>principios y criterios de diseño</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica</t>
+          <t>T6. Artefacto / output</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ideación y conceptualización</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
+          <t>Principios y criterios de diseño</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr"/>
@@ -2508,29 +3378,25 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>acompañamiento a PD/SD</t>
+          <t>ideación y conceptualización</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>X. Modelo de colaboración</t>
+          <t>T4. Técnica</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Acompañamiento a Product / Service Design</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Sacar de la columna</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>No es una capacidad técnica sino un modelo de trabajo. Además es lo único que introduce otras especialidades de diseño en una matriz que decidió evaluar solo diseño conductual. Va en la definición del rol.</t>
-        </is>
-      </c>
+          <t>Ideación y conceptualización</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -2540,25 +3406,29 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>prototipado conceptual</t>
+          <t>acompañamiento a PD/SD</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica</t>
+          <t>X. Modelo de colaboración</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Prototipado conceptual</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr"/>
+          <t>Acompañamiento a Product / Service Design</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Sacar de la columna</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>No es una capacidad técnica sino un modelo de trabajo. Además es lo único que introduce otras especialidades de diseño en una matriz que decidió evaluar solo diseño conductual. Va en la definición del rol.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -2568,29 +3438,25 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>journey &amp; systems thinking</t>
+          <t>prototipado conceptual</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>T5. Marco conceptual</t>
+          <t>T4. Técnica</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Journey thinking / Systems thinking</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Desagregar y unificar</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Son dos lentes distintos, y «systems thinking» ya está en D2. Definir un único hogar.</t>
-        </is>
-      </c>
+          <t>Prototipado conceptual</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -2600,27 +3466,27 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>orquestación de experiencias</t>
+          <t>journey &amp; systems thinking</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>T1. Objetivo / alcance</t>
+          <t>T5. Marco conceptual</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Orquestación de la experiencia a través de touchpoints y canales</t>
+          <t>Journey thinking / Systems thinking</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Reubicar</t>
+          <t>Desagregar y unificar</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Es el alcance del objetivo (una intervención frente a un sistema de intervenciones), y es donde entra de forma natural el campo Híbrido.</t>
+          <t>Son dos lentes distintos, y «systems thinking» ya está en D2. Definir un único hogar.</t>
         </is>
       </c>
     </row>
@@ -2632,91 +3498,91 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>personalización, comunicación y contenido conductual</t>
+          <t>orquestación de experiencias</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>T5b. Palanca de intervención</t>
+          <t>T1. Objetivo / alcance</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Palancas conductuales: fricción, defaults, timing y saliencia, framing y comunicación, incentivos, normas sociales, personalización</t>
+          <t>Orquestación de la experiencia a través de touchpoints y canales</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Desagregar y completar</t>
+          <t>Reubicar</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Hoy se nombran tres palancas sueltas mezcladas con marcos. Conviene una taxonomía explícita de palancas: es lo que hace evaluable el diseño conductual.</t>
+          <t>Es el alcance del objetivo (una intervención frente a un sistema de intervenciones), y es donde entra de forma natural el campo Híbrido.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>4. Experimentación, Medición e Impacto</t>
+          <t>3. Diseño y Orquestación de Experiencias</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Formulación y validación de hipótesis</t>
+          <t>personalización, comunicación y contenido conductual</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>T1 + T4</t>
+          <t>T5b. Palanca de intervención</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Formulación operacional de hipótesis y variables</t>
+          <t>Palancas conductuales: fricción, defaults, timing y saliencia, framing y comunicación, incentivos, normas sociales, personalización</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Desagregar</t>
+          <t>Desagregar y completar</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>«Formular» es técnica; «validar» es el objetivo de toda la dimensión.</t>
+          <t>Hoy se nombran tres palancas sueltas mezcladas con marcos. Conviene una taxonomía explícita de palancas: es lo que hace evaluable el diseño conductual.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>4. Experimentación, Medición e Impacto</t>
+          <t>3. Diseño y Orquestación de Experiencias</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>UX Validatio [sic]</t>
+          <t>— ausente —</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>T1. Objetivo (evaluativo)</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>UX validation: validar concepto, prototipo o experiencia en campo digital</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>Corregir y reubicar</t>
+          <t>Criterio de intervención: cuánta intervención pide la conducta, qué palanca es proporcional y cuándo lo correcto es no intervenir</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Erratum en el archivo original («UX Validatio»). Además es un objetivo, no una técnica: las técnicas que lo sirven son usability y prototype testing.</t>
+          <t>Es la meta-capacidad más importante de un rol que diseña conducta. Sin ella, la matriz premia intervenir y no tiene forma de reconocer la decisión de no hacerlo.</t>
         </is>
       </c>
     </row>
@@ -2728,25 +3594,29 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>concept &amp; prototype testing</t>
+          <t>Formulación y validación de hipótesis</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica</t>
+          <t>T1 + T4</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Concept &amp; prototype testing</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr"/>
+          <t>Formulación operacional de hipótesis y variables</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Desagregar</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>«Formular» es técnica; «validar» es el objetivo de toda la dimensión.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -2756,25 +3626,29 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>experimentación conductual</t>
+          <t>UX Validatio [sic]</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>T3. Metodología</t>
+          <t>T1. Objetivo (evaluativo)</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Experimentación conductual</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr"/>
+          <t>UX validation: validar concepto, prototipo o experiencia en campo digital</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Corregir y reubicar</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Erratum en el archivo original («UX Validatio»). Además es un objetivo, no una técnica: las técnicas que lo sirven son usability y prototype testing.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2784,17 +3658,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>diseño experimental</t>
+          <t>concept &amp; prototype testing</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>T3. Metodología</t>
+          <t>T4. Técnica</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Diseño experimental</t>
+          <t>Concept &amp; prototype testing</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2812,22 +3686,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>métricas y criterios de éxito</t>
+          <t>experimentación conductual</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>T6. Artefacto / output</t>
+          <t>T3. Metodología</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Métricas y criterios de éxito</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
+          <t>Experimentación conductual</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr"/>
@@ -2840,29 +3714,25 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A/B testing</t>
+          <t>diseño experimental</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica</t>
+          <t>T3. Metodología</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>A/B testing y multivariante</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Es una técnica DENTRO del diseño experimental. Hoy está al mismo nivel que «diseño experimental» y que «RCT», lo que impide graduar la progresión de niveles.</t>
-        </is>
-      </c>
+          <t>Diseño experimental</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -2872,29 +3742,25 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>RCT y cuasi-experimentos</t>
+          <t>métricas y criterios de éxito</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>T3. Metodología</t>
+          <t>T6. Artefacto / output</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>RCT · Cuasi-experimentos · Pre-post con grupo de control</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Mantener — desagregar</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>RCT y cuasi-experimento tienen exigencias de validez muy distintas: separarlos permite diferenciar Specialist de Expert.</t>
-        </is>
-      </c>
+          <t>Métricas y criterios de éxito</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -2904,17 +3770,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>métodos cuantitativos</t>
+          <t>A/B testing</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>T2. Enfoque</t>
+          <t>T4. Técnica</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Enfoque cuantitativo</t>
+          <t>A/B testing y multivariante</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -2924,7 +3790,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Es un enfoque, y ya está declarado en D1. Aquí genera redundancia entre dimensiones.</t>
+          <t>Es una técnica DENTRO del diseño experimental. Hoy está al mismo nivel que «diseño experimental» y que «RCT», lo que impide graduar la progresión de niveles.</t>
         </is>
       </c>
     </row>
@@ -2936,25 +3802,29 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>RCT y cuasi-experimentos</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>T4. Técnica / fuente de datos</t>
+          <t>T3. Metodología</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Analytics e instrumentación de producto</t>
+          <t>RCT · Cuasi-experimentos · Pre-post con grupo de control</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr"/>
+          <t>Mantener — desagregar</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>RCT y cuasi-experimento tienen exigencias de validez muy distintas: separarlos permite diferenciar Specialist de Expert.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -2964,17 +3834,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>control de variables</t>
+          <t>métodos cuantitativos</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>T7. Calidad</t>
+          <t>T2. Enfoque</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Control de variables; validez interna</t>
+          <t>Enfoque cuantitativo</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -2984,7 +3854,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Es un criterio de validez, no una técnica autónoma.</t>
+          <t>Es un enfoque, y ya está declarado en D1. Aquí genera redundancia entre dimensiones.</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3866,25 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>inferencia causal</t>
+          <t>analytics</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>T5. Marco conceptual</t>
+          <t>T4. Técnica / fuente de datos</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Inferencia causal</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Es la lógica que justifica el diseño, no un método aplicable por sí solo.</t>
-        </is>
-      </c>
+          <t>Analytics e instrumentación de producto</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -3028,27 +3894,27 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>triangulación</t>
+          <t>control de variables</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>T7. Calidad (aquí) / T4 (en D1)</t>
+          <t>T7. Calidad</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Triangulación como criterio de robustez de resultados</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>Resolver duplicado</t>
+          <t>Control de variables; validez interna</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Segunda aparición. Definir un único hogar y, si se repite, que sea con función distinta y explícita.</t>
+          <t>Es un criterio de validez, no una técnica autónoma.</t>
         </is>
       </c>
     </row>
@@ -3060,17 +3926,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>evaluación de impacto</t>
+          <t>inferencia causal</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>T1. Objetivo</t>
+          <t>T5. Marco conceptual</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Evaluación de impacto</t>
+          <t>Inferencia causal</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -3080,7 +3946,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Objetivo de máxima exigencia causal. Debe encabezar la dimensión junto a «validación».</t>
+          <t>Es la lógica que justifica el diseño, no un método aplicable por sí solo.</t>
         </is>
       </c>
     </row>
@@ -3092,27 +3958,27 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>continuous learning</t>
+          <t>triangulación</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>Y. Resultado organizacional</t>
+          <t>T7. Calidad (aquí) / T4 (en D1)</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Evidencia acumulativa y aprendizaje continuo</t>
+          <t>Triangulación como criterio de robustez de resultados</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Sacar de la columna</t>
+          <t>Resolver duplicado</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Es un estado deseado de la organización, no una capacidad individual evaluable. Su hogar natural es la Dimensión 5.</t>
+          <t>Segunda aparición. Definir un único hogar y, si se repite, que sea con función distinta y explícita.</t>
         </is>
       </c>
     </row>
@@ -3124,27 +3990,27 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>— ausente —</t>
+          <t>evaluación de impacto</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>T7. Ética</t>
+          <t>T1. Objetivo</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Ética experimental: consentimiento, grupos de control, reversibilidad de la intervención</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>Añadir (gap)</t>
+          <t>Evaluación de impacto</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>GAP: experimentar con la conducta real de clientes sin criterio ético explícito es el mayor riesgo reputacional de la unificación de roles.</t>
+          <t>Objetivo de máxima exigencia causal. Debe encabezar la dimensión junto a «validación».</t>
         </is>
       </c>
     </row>
@@ -3156,117 +4022,125 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>— ausente —</t>
+          <t>continuous learning</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>T3. Metodología — campo físico</t>
+          <t>Y. Resultado organizacional</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Piloto en campo; cuasi-experimento por sede o territorio</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>Añadir (gap)</t>
+          <t>Evidencia acumulativa y aprendizaje continuo</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Sacar de la columna</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>GAP: toda la dimensión está escrita desde el campo digital.</t>
+          <t>Es un estado deseado de la organización, no una capacidad individual evaluable. Su hogar natural es la Dimensión 5.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>5. Escalamiento y Liderazgo</t>
+          <t>4. Experimentación, Medición e Impacto</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ResearchOps</t>
+          <t>— ausente —</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>T8. Práctica operativa</t>
+          <t>T7. Ética</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>ResearchOps</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr"/>
+          <t>Ética experimental: consentimiento, grupos de control, reversibilidad de la intervención</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>GAP: experimentar con la conducta real de clientes sin criterio ético explícito es el mayor riesgo reputacional de la unificación de roles.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>5. Escalamiento y Liderazgo</t>
+          <t>4. Experimentación, Medición e Impacto</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>BehavioralOps</t>
+          <t>— ausente —</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>T8. Práctica operativa</t>
+          <t>T3. Metodología — campo físico</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>BehavioralOps</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Mantener — definir</t>
+          <t>Piloto en campo; cuasi-experimento por sede o territorio</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Es el término menos estandarizado de la matriz. Conviene definirlo explícitamente (catálogo de intervenciones, reutilización, medición acumulada) para que sea evaluable.</t>
+          <t>GAP: toda la dimensión está escrita desde el campo digital.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>5. Escalamiento y Liderazgo</t>
+          <t>4. Experimentación, Medición e Impacto</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>KnowledgeOps</t>
+          <t>— ausente —</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>T8. Práctica operativa</t>
+          <t>T0. Meta-capacidad</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>KnowledgeOps</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr"/>
+          <t>Criterio de evidencia: cuánto rigor exige cada decisión y cuánto sería desperdiciarlo</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Sin esta meta-capacidad, «más rigor» se lee siempre como «mejor», y la matriz no puede reconocer el juicio de proporcionalidad, que es justo lo que distingue a un Expert.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -3276,7 +4150,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>gestión y activación del conocimiento</t>
+          <t>ResearchOps</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -3286,19 +4160,15 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Gestión y activación del conocimiento</t>
+          <t>ResearchOps</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Mantener — posible absorción</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Se solapa con KnowledgeOps: decidir si es su contenido o una práctica distinta.</t>
-        </is>
-      </c>
+          <t>Mantener</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -3308,27 +4178,27 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>estándares y gobernanza</t>
+          <t>BehavioralOps</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>T7 + T8</t>
+          <t>T8. Práctica operativa</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Estándares metodológicos; gobernanza de datos y privacidad</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Desagregar</t>
+          <t>BehavioralOps</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Mantener — definir</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Estándar (calidad) y gobernanza (decisión y control) son cosas distintas.</t>
+          <t>Es el término menos estandarizado de la matriz. Conviene definirlo explícitamente (catálogo de intervenciones, reutilización, medición acumulada) para que sea evaluable.</t>
         </is>
       </c>
     </row>
@@ -3340,22 +4210,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>stakeholder management</t>
+          <t>KnowledgeOps</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>T9. Competencia transversal</t>
+          <t>T8. Práctica operativa</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Stakeholder management</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
+          <t>KnowledgeOps</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr"/>
@@ -3368,25 +4238,29 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>influencia</t>
+          <t>gestión y activación del conocimiento</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>T9. Competencia transversal</t>
+          <t>T8. Práctica operativa</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Influencia</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr"/>
+          <t>Gestión y activación del conocimiento</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Mantener — posible absorción</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Se solapa con KnowledgeOps: decidir si es su contenido o una práctica distinta.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -3396,25 +4270,29 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>facilitación</t>
+          <t>estándares y gobernanza</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>T9. Competencia transversal</t>
+          <t>T7 + T8</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Facilitación</t>
+          <t>Estándares metodológicos; gobernanza de datos y privacidad</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Reubicar</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr"/>
+          <t>Desagregar</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Estándar (calidad) y gobernanza (decisión y control) son cosas distintas.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -3424,7 +4302,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>mentoring</t>
+          <t>stakeholder management</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -3434,7 +4312,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Mentoring</t>
+          <t>Stakeholder management</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -3452,29 +4330,25 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>capability building</t>
+          <t>influencia</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>T8. Práctica operativa</t>
+          <t>T9. Competencia transversal</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Capability building</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Mantener</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Distinguir de «mentoring»: mentoring es uno a uno, capability building es sistémico.</t>
-        </is>
-      </c>
+          <t>Influencia</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -3484,17 +4358,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>gestión de calidad</t>
+          <t>facilitación</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>T7. Calidad</t>
+          <t>T9. Competencia transversal</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Gestión de calidad</t>
+          <t>Facilitación</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -3512,7 +4386,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>priorización</t>
+          <t>mentoring</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -3522,19 +4396,15 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Priorización de portafolio de estudios e intervenciones</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>Reubicar — precisar</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>«Priorización» a secas ya aparece implícita en D2. Aquí debe significar priorización de portafolio.</t>
-        </is>
-      </c>
+          <t>Reubicar</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -3544,27 +4414,27 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>comunicación estratégica</t>
+          <t>capability building</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>T9. Competencia transversal</t>
+          <t>T8. Práctica operativa</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Comunicación estratégica</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>Reubicar</t>
+          <t>Capability building</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Mantener</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Se solapa con «storytelling estratégico» de D2: definir un único hogar.</t>
+          <t>Distinguir de «mentoring»: mentoring es uno a uno, capability building es sistémico.</t>
         </is>
       </c>
     </row>
@@ -3576,29 +4446,25 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>cultura de evidencia</t>
+          <t>gestión de calidad</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Y. Resultado organizacional</t>
+          <t>T7. Calidad</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Cultura de decisión basada en evidencia</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>Sacar de la columna</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Es el propósito de la dimensión, no una capacidad. Ya está dicho en «Definición para el rol».</t>
-        </is>
-      </c>
+          <t>Gestión de calidad</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -3608,28 +4474,220 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
+          <t>priorización</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>T9. Competencia transversal</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Priorización de portafolio de estudios e intervenciones</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar — precisar</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>«Priorización» a secas ya aparece implícita en D2. Aquí debe significar priorización de portafolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>comunicación estratégica</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>T9. Competencia transversal</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Comunicación estratégica</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Reubicar</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Se solapa con «storytelling estratégico» de D2: definir un único hogar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>cultura de evidencia</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Y. Resultado organizacional</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Cultura de decisión basada en evidencia</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Sacar de la columna</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Es el propósito de la dimensión, no una capacidad. Ya está dicho en «Definición para el rol».</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
           <t>mejora continua</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>T8. Práctica operativa</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Mejora continua</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>Mantener</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>— ausente —</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>T0. Meta-capacidad</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Criterio de escalamiento y liderazgo: qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>La dimensión enumera prácticas de Ops y competencias, pero no la capacidad de decidir entre ellas ni de calibrar la exigencia sobre el equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>— ausente —</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>T7b. Ética del liderazgo — EQUILIBRIO</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>La dimensión mide lo que el liderazgo PRODUCE (estándares, gobernanza, capacidades) pero no cómo trata a quienes lo hacen posible. Sin el contrapeso de la satisfacción, «capability building» y «mejora continua» premian a quien exprime al equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>5. Escalamiento y Liderazgo</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>— ausente —</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>T7b. Ética del liderazgo — UMBRAL</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Respeto básico: sin acoso, sin mansplaining, sin conductas excluyentes. Se verifica; no se pondera</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>Añadir (gap)</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>No es una variable del equilibrio: es un piso. Si entrara en la ponderación 30/20/15/20/15, la matriz estaría diciendo que un buen resultado puede compensarlo. Su incumplimiento verificado bloquea el nivel.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F71"/>
+  <autoFilter ref="A4:F77"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -3638,7 +4696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3695,17 +4753,17 @@
           <t>1. Discovery e Insights</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Problem framing &amp; Research Strategy: estrategia de investigación,  investigación cualitativa, cuantitativa y mixta,  UX Research, Behavioral Research, desk research, muestreo,  diagnóstico conductual y sistémico, triangulación, síntesis, generación de insights, calidad de evidencia</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar.
+          <t>T0 META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar. ¿Es esta la investigación que la decisión necesita, o solo la que sabemos hacer?
 T1 OBJETIVO · Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
 T2 ENFOQUE · Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
 T3 METODOLOGÍA · Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
@@ -3723,17 +4781,18 @@
           <t>2. Estrategia y Problem Solving</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Síntesis estratégica; problem reframing; frameworks de Research, Design y Behavioral Science; system thinking; business acumen; opportunity framing, formulación y priorización de hipótesis; evaluación de valor y viabilidad; pensamiento crítico; ética; storytelling estratégico.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
+          <t>T0 META-CAPACIDAD · Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
+T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
 T5 MARCO · Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio.
 T4 TÉCNICA (análisis y decisión) · Síntesis estratégica; evaluación de valor, viabilidad, riesgo y esfuerzo; matrices de priorización; exploración de escenarios y trade-offs.
 T6 ARTEFACTO · Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica.
@@ -3748,10 +4807,10 @@
           <t>3. Diseño y Orquestación de Experiencias</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Diseño de intervenciones conductuales; arquitectura de decisiones; traducción de insights a diseño; principios y criterios de diseño; ideación y conceptualización; acompañamiento a PD/SD; prototipado conceptual; journey &amp; systems thinking; orquestación de experiencias; personalización, comunicación y contenido conductual</t>
         </is>
@@ -3759,6 +4818,7 @@
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>E3 ESPECIALIDAD · Diseño conductual (única especialidad de diseño evaluada por esta matriz).
+T0 META-CAPACIDAD · Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
 T1 OBJETIVO · Traducir evidencia y estrategia en principios, conceptos e intervenciones; intervenir sobre una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
 T5 MARCO · Arquitectura de decisiones; journey thinking; systems thinking.
 T5b PALANCAS DE INTERVENCIÓN · Fricción y esfuerzo; defaults; timing y saliencia; framing y comunicación conductual; incentivos; normas sociales; personalización.
@@ -3775,17 +4835,18 @@
           <t>4. Experimentación, Medición e Impacto</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Formulación y validación de  hipótesis: UX Validatio,  concept &amp; prototype testing; experimentación conductual; diseño experimental; métricas y criterios de éxito; A/B testing; RCT y cuasi-experimentos; métodos cuantitativos; analytics; control de variables; inferencia causal; triangulación; evaluación de impacto; continuous learning.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
+          <t>T0 META-CAPACIDAD · Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
+T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
 T2 ENFOQUE · Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto.
 T3 METODOLOGÍA · Diseño experimental; RCT; cuasi-experimentos; pre-post con grupo de control; pruebas de concepto y prototipo; piloto en campo (físico) y en producto (digital).
 T4 TÉCNICA · Formulación operacional de hipótesis y variables; A/B testing y multivariante; concept &amp; prototype testing; usability testing; analytics e instrumentación; análisis estadístico.
@@ -3801,19 +4862,21 @@
           <t>5. Escalamiento y Liderazgo</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>ResearchOps; BehavioralOps; KnowledgeOps; gestión y activación del conocimiento; estándares y gobernanza; stakeholder management; influencia; facilitación; mentoring; capability building; gestión de calidad; priorización; comunicación estratégica; cultura de evidencia; mejora continua.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
+          <t>T0 META-CAPACIDAD · Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
+T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
 T8 PRÁCTICA OPERATIVA · ResearchOps; BehavioralOps; KnowledgeOps; gestión y activación del conocimiento; repositorios y trazabilidad; automatización; capability building; mejora continua.
 T7 GOBERNANZA, CALIDAD Y ÉTICA · Estándares metodológicos; gobernanza de datos y privacidad; gestión de calidad; ética aplicada.
+T7b ÉTICA DEL LIDERAZGO · Se mide en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico — sin acoso, sin mansplaining, sin conductas excluyentes. El umbral no entra en la ponderación: su incumplimiento verificado bloquea el nivel. Ver hoja «4. Ética del liderazgo».
 T6 ARTEFACTO · Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council.
 T9 COMPETENCIA · Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
         </is>
@@ -3828,7 +4891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3866,7 +4929,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Alcance — Campos de investigación: Digital (UX) · Físico · Híbrido [· Sistémico / contextual, a decidir].     Única especialidad de diseño evaluada: Diseño Conductual.     Product Design y Service Design aparecen solo como modelo de colaboración.</t>
         </is>
@@ -3940,12 +5003,12 @@
           <t>1. Discovery e Insights</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="21" t="n">
         <v>0.3</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar.
+          <t>T0 META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar. ¿Es esta la investigación que la decisión necesita, o solo la que sabemos hacer?
 T1 OBJETIVO · Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
 T2 ENFOQUE · Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
 T3 METODOLOGÍA · Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
@@ -4008,12 +5071,13 @@
           <t>2. Estrategia y Problem Solving</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.2</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
+          <t>T0 META-CAPACIDAD · Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
+T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
 T5 MARCO · Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio.
 T4 TÉCNICA (análisis y decisión) · Síntesis estratégica; evaluación de valor, viabilidad, riesgo y esfuerzo; matrices de priorización; exploración de escenarios y trade-offs.
 T6 ARTEFACTO · Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica.
@@ -4073,12 +5137,13 @@
           <t>3. Diseño y Orquestación de Experiencias</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.15</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>E3 ESPECIALIDAD · Diseño conductual (única especialidad de diseño evaluada por esta matriz).
+T0 META-CAPACIDAD · Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
 T1 OBJETIVO · Traducir evidencia y estrategia en principios, conceptos e intervenciones; intervenir sobre una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
 T5 MARCO · Arquitectura de decisiones; journey thinking; systems thinking.
 T5b PALANCAS DE INTERVENCIÓN · Fricción y esfuerzo; defaults; timing y saliencia; framing y comunicación conductual; incentivos; normas sociales; personalización.
@@ -4140,12 +5205,13 @@
           <t>4. Experimentación, Medición e Impacto</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.2</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
+          <t>T0 META-CAPACIDAD · Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
+T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
 T2 ENFOQUE · Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto.
 T3 METODOLOGÍA · Diseño experimental; RCT; cuasi-experimentos; pre-post con grupo de control; pruebas de concepto y prototipo; piloto en campo (físico) y en producto (digital).
 T4 TÉCNICA · Formulación operacional de hipótesis y variables; A/B testing y multivariante; concept &amp; prototype testing; usability testing; analytics e instrumentación; análisis estadístico.
@@ -4206,14 +5272,16 @@
           <t>5. Escalamiento y Liderazgo</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.15</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
+          <t>T0 META-CAPACIDAD · Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
+T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
 T8 PRÁCTICA OPERATIVA · ResearchOps; BehavioralOps; KnowledgeOps; gestión y activación del conocimiento; repositorios y trazabilidad; automatización; capability building; mejora continua.
 T7 GOBERNANZA, CALIDAD Y ÉTICA · Estándares metodológicos; gobernanza de datos y privacidad; gestión de calidad; ética aplicada.
+T7b ÉTICA DEL LIDERAZGO · Se mide en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico — sin acoso, sin mansplaining, sin conductas excluyentes. El umbral no entra en la ponderación: su incumplimiento verificado bloquea el nivel. Ver hoja «4. Ética del liderazgo».
 T6 ARTEFACTO · Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council.
 T9 COMPETENCIA · Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
         </is>
@@ -4275,13 +5343,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4366,7 +5434,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Ordenar cada celda por los niveles T1→T9 (ver hoja «4. Columna C propuesta»).</t>
+          <t>Ordenar cada celda por los niveles T1→T9 (ver hoja «6. Columna C propuesta»).</t>
         </is>
       </c>
     </row>
@@ -4658,170 +5726,260 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>La meta-capacidad existía en una sola dimensión</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>D1 la tenía; D2, D3, D4 y D5 no</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>«Research Strategy» es lo único parecido a una meta-capacidad en toda la matriz, y aun así está escrito como un ítem más de la enumeración, al lado de «muestreo».</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Sin meta-capacidad, la progresión Professional→Master se lee como acumulación: «conoce más frameworks», «sabe más técnicas», «usa más rigor». Lo que separa a un Expert no es ejecutar más, es elegir mejor — y eso no estaba en ninguna parte.</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Declarar una meta-capacidad por dimensión (T0), por encima de T1, y anclar en ella la progresión Specialist→Expert. Ver hoja «3. Meta-capacidades».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>El liderazgo se mide por lo que produce, no por cómo trata al equipo</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>D5 y niveles 3–4 de todas las dimensiones</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>D5 evalúa estándares, gobernanza, capability building y mejora continua. No hay un solo indicador sobre la experiencia de las personas lideradas.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Tal como está, «capability building» y «mejora continua» premian a quien exprime al equipo igual que a quien lo desarrolla: el resultado se ve, el costo humano no. Y en una matriz de un rol que diseña conducta ajena, no medir la propia conducta hacia el equipo es una contradicción difícil de sostener.</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Añadir T7b en dos partes: EQUILIBRIO productividad ↔ satisfacción del equipo (se pondera) sobre un UMBRAL de respeto básico (se verifica, bloquea el nivel). Ver hoja «4. Ética del liderazgo».</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Decisiones pendientes para cerrar con los leads</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Pregunta</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Contexto</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Recomendación</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="100" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>¿Se abre un cuarto campo «Sistémico / contextual»?</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Es el único candidato con criterio propio: cubre lo que no ocurre en un canal (mercado, regulación, ecosistema, evidencia publicada). Sin él, «desk research» y el «diagnóstico sistémico» que ya están en la matriz quedan sin campo asignable. «Organizacional» y «conversacional» NO deberían abrirse: el primero es un sujeto, el segundo cae dentro de híbrido.</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Recomendación: abrirlo, y mantener el sujeto (cliente / colaborador / asesor) como eje separado.</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="n"/>
-    </row>
-    <row r="20" ht="100" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>¿La progresión 1→4 se ancla en metodología o en técnica?</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Hoy la columna mezcla ambas, así que la progresión se puede leer como «sabe más técnicas». Un modelo más defendible: el nivel sube con la exigencia metodológica y con la ambigüedad del problema, no con el número de herramientas.</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Recomendación: anclar en T1 (complejidad del objetivo) y T3 (exigencia metodológica).</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="n"/>
+      <c r="F20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="100" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>¿«Estrategia de investigación» es un ítem o una meta-capacidad?</t>
+          <t>¿Se abre un cuarto campo «Sistémico / contextual»?</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Es la capacidad de componer objetivo + enfoque + metodología + técnica. Listarla junto a «muestreo» la iguala a un instrumento.</t>
+          <t>Es el único candidato con criterio propio: cubre lo que no ocurre en un canal (mercado, regulación, ecosistema, evidencia publicada). Sin él, «desk research» y el «diagnóstico sistémico» que ya están en la matriz quedan sin campo asignable. «Organizacional» y «conversacional» NO deberían abrirse: el primero es un sujeto, el segundo cae dentro de híbrido.</t>
         </is>
       </c>
       <c r="D21" s="14" t="n"/>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Recomendación: declararla meta-capacidad de D1 y hacerla el eje de la progresión Specialist→Expert.</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="n"/>
+          <t>Recomendación: abrirlo, y mantener el sujeto (cliente / colaborador / asesor) como eje separado.</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="n"/>
     </row>
     <row r="22" ht="100" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>¿Las competencias transversales (T9) viven dentro de las dimensiones o en un eje propio?</t>
+          <t>¿La progresión 1→4 se ancla en metodología o en técnica?</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Hoy están repartidas: pensamiento crítico y business acumen en D2; influencia y facilitación en D5. Con pesos por dimensión, su valor depende de dónde caigan.</t>
+          <t>Hoy la columna mezcla ambas, así que la progresión se puede leer como «sabe más técnicas». Un modelo más defendible: el nivel sube con la exigencia metodológica y con la ambigüedad del problema, no con el número de herramientas.</t>
         </is>
       </c>
       <c r="D22" s="14" t="n"/>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Recomendación: mantenerlas dentro de cada dimensión pero marcadas como T9, para que se vea que no compiten con la capacidad metodológica.</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="n"/>
+          <t>Recomendación: anclar en T1 (complejidad del objetivo) y T3 (exigencia metodológica).</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="n"/>
     </row>
     <row r="23" ht="100" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>¿El campo (E1) se evalúa o solo se declara?</t>
+          <t>¿«Estrategia de investigación» es un ítem o una meta-capacidad?</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Si el campo es solo una etiqueta, la matriz sigue siendo digital-first. Si se evalúa, hay que decidir si un Expert debe demostrar solvencia en más de un campo.</t>
+          <t>Es la capacidad de componer objetivo + enfoque + metodología + técnica. Listarla junto a «muestreo» la iguala a un instrumento.</t>
         </is>
       </c>
       <c r="D23" s="14" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
+          <t>Recomendación: declararla meta-capacidad de D1 y hacerla el eje de la progresión Specialist→Expert.</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>¿Las competencias transversales (T9) viven dentro de las dimensiones o en un eje propio?</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Hoy están repartidas: pensamiento crítico y business acumen en D2; influencia y facilitación en D5. Con pesos por dimensión, su valor depende de dónde caigan.</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Recomendación: mantenerlas dentro de cada dimensión pero marcadas como T9, para que se vea que no compiten con la capacidad metodológica.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="n"/>
+    </row>
+    <row r="25" ht="100" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>¿El campo (E1) se evalúa o solo se declara?</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Si el campo es solo una etiqueta, la matriz sigue siendo digital-first. Si se evalúa, hay que decidir si un Expert debe demostrar solvencia en más de un campo.</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
           <t>Recomendación: exigir un campo a Specialist, dos a Expert, y visión híbrida a Master.</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n"/>
+      <c r="F25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>¿Quién administra la medición de la ética del liderazgo, y quién ve el resultado?</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Es la decisión que hace que el sistema funcione o se vuelva decorativo. El acceso al resultado desagregado, el n mínimo para publicar y el momento de entrega tienen que quedar definidos ANTES de la primera medición: si se deciden después de conocer los resultados, el instrumento pierde credibilidad ante el equipo y nadie vuelve a responder con honestidad.</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Recomendación: Personas administra el instrumento y custodia el anonimato; el Council define los indicadores; el resultado agregado se comparte con el equipo que respondió. El n mínimo (≥5) y la regla de bloqueo se publican de antemano.</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>

--- a/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
+++ b/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
@@ -710,10 +710,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="51" customHeight="1">
+    <row r="16" ht="111" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>T0 Meta-capacidad → T1 Objetivo → T2 Enfoque → T3 Metodología → T4 Técnica → T5 Marco conceptual → T6 Artefacto → T7 Calidad y ética (T7b Ética del liderazgo donde corresponde) → T8 Práctica operativa → T9 Competencia transversal.</t>
+          <t>Las cinco dimensiones usan la MISMA estructura de nueve campos, siempre en este orden y sin excepciones:
+  META-CAPACIDAD → OBJETIVO → ENFOQUE → METODOLOGÍA → TÉCNICA → MARCO → ARTEFACTO → CALIDAD Y ÉTICA → COMPETENCIAS
+Que la estructura sea idéntica es lo que hace comparables las cinco dimensiones entre sí: si un campo estuviera en unas y no en otras, la comparación volvería a depender de cómo esté redactada cada celda.
+Dos integraciones para no romper la estructura: las palancas conductuales de D3 viven dentro de TÉCNICA (son el instrumento de la intervención), y ResearchOps, BehavioralOps y KnowledgeOps de D5 viven dentro de METODOLOGÍA (son la forma de estructurar el trabajo, no un instrumento suelto).</t>
         </is>
       </c>
     </row>
@@ -4763,15 +4766,15 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar. ¿Es esta la investigación que la decisión necesita, o solo la que sabemos hacer?
-T1 OBJETIVO · Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
-T2 ENFOQUE · Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
-T3 METODOLOGÍA · Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
-T4 TÉCNICA · Recolección: entrevistas, observación estructurada, diarios, encuestas, intercept y mystery shopping (campo físico), analítica de comportamiento. Análisis: diseño muestral, codificación, triangulación de métodos y fuentes, síntesis.
-T5 MARCO · Frameworks de ciencias del comportamiento para leer conducta (COM-B, EAST); systems thinking.
-T6 ARTEFACTO · Insight; plan y estrategia de investigación.
-T7 CALIDAD Y ÉTICA · Calidad y suficiencia de la evidencia; gestión de sesgos; límites de validez; consentimiento y privacidad.
-T9 COMPETENCIA · Pensamiento crítico.</t>
+          <t>META-CAPACIDAD: Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar.
+OBJETIVO: Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
+ENFOQUE: Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
+METODOLOGÍA: Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
+TÉCNICA: Recolección: entrevistas, observación estructurada, diarios, encuestas, intercept y mystery shopping (campo físico), analítica de comportamiento. Análisis: diseño muestral, codificación, triangulación de métodos y fuentes, síntesis.
+MARCO: Frameworks de ciencias del comportamiento para leer conducta (COM-B, EAST); systems thinking.
+ARTEFACTO: Insight; plan y estrategia de investigación.
+CALIDAD Y ÉTICA: Calidad y suficiencia de la evidencia; gestión de sesgos; límites de validez; consentimiento y privacidad.
+COMPETENCIAS: Pensamiento crítico.</t>
         </is>
       </c>
     </row>
@@ -4791,13 +4794,15 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
-T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
-T5 MARCO · Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio.
-T4 TÉCNICA (análisis y decisión) · Síntesis estratégica; evaluación de valor, viabilidad, riesgo y esfuerzo; matrices de priorización; exploración de escenarios y trade-offs.
-T6 ARTEFACTO · Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica.
-T7 CALIDAD Y ÉTICA · Supuestos explícitos; estándar de evidencia exigible según el tipo de decisión; ética de la intervención.
-T9 COMPETENCIA · Pensamiento crítico; business acumen; storytelling estratégico.</t>
+          <t>META-CAPACIDAD: Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
+OBJETIVO: Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas; definición de direcciones y de trade-offs.
+ENFOQUE: Integración de la evidencia de usuario, de comportamiento y de negocio; lectura divergente para abrir alternativas y convergente para cerrar la decisión; evidencia primaria, secundaria y de mercado.
+METODOLOGÍA: Síntesis estratégica sobre evidencia acumulada; análisis del espacio de problema y de oportunidades; análisis de escenarios; modelado de sistemas y de actores.
+TÉCNICA: Encuadre: árboles de problema, reformulación de la pregunta, mapas de oportunidad. Decisión: matrices de priorización, evaluación de valor, viabilidad, riesgo y esfuerzo, análisis de trade-offs, pre-mortem.
+MARCO: Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio; modelos de negocio y de valor.
+ARTEFACTO: Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica de la decisión.
+CALIDAD Y ÉTICA: Supuestos explícitos y trazables; estándar de evidencia exigible según el tipo de decisión; declaración del riesgo de equivocarse; ética de la intervención propuesta.
+COMPETENCIAS: Pensamiento crítico; business acumen; storytelling estratégico.</t>
         </is>
       </c>
     </row>
@@ -4817,15 +4822,15 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>E3 ESPECIALIDAD · Diseño conductual (única especialidad de diseño evaluada por esta matriz).
-T0 META-CAPACIDAD · Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
-T1 OBJETIVO · Traducir evidencia y estrategia en principios, conceptos e intervenciones; intervenir sobre una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
-T5 MARCO · Arquitectura de decisiones; journey thinking; systems thinking.
-T5b PALANCAS DE INTERVENCIÓN · Fricción y esfuerzo; defaults; timing y saliencia; framing y comunicación conductual; incentivos; normas sociales; personalización.
-T4 TÉCNICA · Ideación y conceptualización; traducción de insights a criterios de diseño; prototipado conceptual; behavioral walkthrough; diseño de contenido conductual.
-T6 ARTEFACTO · Principios y criterios de diseño; concepto de intervención; blueprint de orquestación.
-T7 CALIDAD Y ÉTICA · Ética de la influencia (transparencia, autonomía de la persona, no explotación de sesgos); testeabilidad de la intervención.
-X MODELO DE COLABORACIÓN (no es capacidad; describe alcance) · Acompañamiento a Product y Service Design en la conceptualización y orquestación de la experiencia.</t>
+          <t>META-CAPACIDAD: Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
+OBJETIVO: Traducir evidencia y estrategia en principios, conceptos e intervenciones; modificar una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
+ENFOQUE: Diseño conductual, única especialidad de diseño de la matriz. Se diseña sobre conducta observada y no sobre conducta declarada; intervención puntual frente a sistema de intervenciones; reducir fricción frente a añadir refuerzo.
+METODOLOGÍA: Diseño de intervenciones conductuales; arquitectura de decisiones aplicada a un journey; ciclos iterativos de concepto, prueba y ajuste; co-diseño con las áreas dueñas de la experiencia.
+TÉCNICA: Palancas: fricción y esfuerzo, defaults, timing y saliencia, framing y comunicación conductual, incentivos, normas sociales, personalización. Proceso: traducción de insights a criterios de diseño, ideación y conceptualización, prototipado conceptual, behavioral walkthrough, diseño de contenido conductual.
+MARCO: Arquitectura de decisiones; journey thinking; systems thinking; taxonomías de palancas y de sesgos.
+ARTEFACTO: Principios y criterios de diseño; concepto de intervención; prototipo conceptual; blueprint de orquestación; hipótesis conductual lista para validar.
+CALIDAD Y ÉTICA: Ética de la influencia — transparencia, autonomía de la persona, no explotación de sesgos, reversibilidad de la intervención; proporcionalidad entre el problema y la palanca; testeabilidad; equidad del efecto entre segmentos.
+COMPETENCIAS: Pensamiento crítico aplicado al propio diseño; comunicación visual y narrativa del concepto; escucha y traducción entre disciplinas.</t>
         </is>
       </c>
     </row>
@@ -4845,14 +4850,15 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
-T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
-T2 ENFOQUE · Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto.
-T3 METODOLOGÍA · Diseño experimental; RCT; cuasi-experimentos; pre-post con grupo de control; pruebas de concepto y prototipo; piloto en campo (físico) y en producto (digital).
-T4 TÉCNICA · Formulación operacional de hipótesis y variables; A/B testing y multivariante; concept &amp; prototype testing; usability testing; analytics e instrumentación; análisis estadístico.
-T5 MARCO · Inferencia causal; teoría del cambio; jerarquía de evidencia.
-T6 ARTEFACTO · Hipótesis operacionalizada; métricas y criterios de éxito; lectura de resultados y recomendación de decisión.
-T7 CALIDAD Y ÉTICA · Validez interna y externa; control de variables; potencia y tamaño muestral; triangulación como criterio de robustez; ética experimental (consentimiento, grupos de control, reversibilidad).</t>
+          <t>META-CAPACIDAD: Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
+OBJETIVO: UX validation (concepto, prototipo, experiencia); evaluación del efecto de las intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
+ENFOQUE: Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto; medición en condiciones controladas frente a medición en condiciones reales.
+METODOLOGÍA: Diseño experimental; RCT; cuasi-experimentos por sede, territorio o cohorte; pre-post con grupo de control; pruebas de concepto y de prototipo; piloto en campo (físico) y en producto (digital).
+TÉCNICA: Diseño: operacionalización de hipótesis y variables, definición de grupos y regla de asignación, cálculo de tamaño muestral. Ejecución y análisis: A/B testing y multivariante, concept &amp; prototype testing, usability testing, analytics e instrumentación, análisis estadístico y por segmentos.
+MARCO: Inferencia causal; teoría del cambio; jerarquía de evidencia; modelo lógico de la intervención (el mecanismo por el que se espera que funcione).
+ARTEFACTO: Hipótesis operacionalizada; métricas y criterios de éxito definidos antes de medir; lectura de resultados con tamaño de efecto; recomendación de decisión.
+CALIDAD Y ÉTICA: Validez interna y externa; control de variables; potencia y tamaño muestral; triangulación como criterio de robustez; ética experimental — consentimiento, uso de grupos de control, reversibilidad y no daño al grupo no expuesto.
+COMPETENCIAS: Honestidad intelectual ante resultados negativos; comunicación de la incertidumbre; rigor en la lectura de datos ajenos.</t>
         </is>
       </c>
     </row>
@@ -4872,13 +4878,15 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
-T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
-T8 PRÁCTICA OPERATIVA · ResearchOps; BehavioralOps; KnowledgeOps; gestión y activación del conocimiento; repositorios y trazabilidad; automatización; capability building; mejora continua.
-T7 GOBERNANZA, CALIDAD Y ÉTICA · Estándares metodológicos; gobernanza de datos y privacidad; gestión de calidad; ética aplicada.
-T7b ÉTICA DEL LIDERAZGO · Se mide en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico — sin acoso, sin mansplaining, sin conductas excluyentes. El umbral no entra en la ponderación: su incumplimiento verificado bloquea el nivel. Ver hoja «4. Ética del liderazgo».
-T6 ARTEFACTO · Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council.
-T9 COMPETENCIA · Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
+          <t>META-CAPACIDAD: Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
+OBJETIVO: Escalar conocimiento, prácticas y capacidades; desarrollar personas; sostener una cultura de decisión basada en evidencia.
+ENFOQUE: Evidencia acumulativa frente a estudio aislado; estandarizar frente a dejar variar; construir capacidad interna frente a resolver por encargo.
+METODOLOGÍA: ResearchOps, BehavioralOps y KnowledgeOps como sistemas de trabajo; gobernanza de estándares y de datos; capability building y modelos de desarrollo de personas; mejora continua.
+TÉCNICA: Conocimiento: repositorios y taxonomías de evidencia, activación y democratización del conocimiento, automatización de tareas operativas, trazabilidad. Liderazgo y equipo: feedback ascendente anónimo, observación estructurada de reuniones (habla, interrupciones y atribución de ideas), registro de asignación de oportunidades visibles, planes de desarrollo, entrevista de salida.
+MARCO: Systems thinking aplicado a la propia capacidad; modelo de madurez de la práctica; ciclo de mejora continua; el propio marco conductual aplicado al equipo — la conducta de quien lidera también es conducta observable.
+ARTEFACTO: Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council; tablero del equilibrio productividad–satisfacción del equipo.
+CALIDAD Y ÉTICA: Estándares metodológicos; gobernanza de datos, privacidad y trazabilidad; gestión de calidad. Ética del liderazgo, en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico, sin acoso, sin mansplaining, sin conductas excluyentes; su incumplimiento verificado bloquea el nivel y no entra en la ponderación.
+COMPETENCIAS: Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
         </is>
       </c>
     </row>
@@ -5008,15 +5016,15 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar. ¿Es esta la investigación que la decisión necesita, o solo la que sabemos hacer?
-T1 OBJETIVO · Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
-T2 ENFOQUE · Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
-T3 METODOLOGÍA · Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
-T4 TÉCNICA · Recolección: entrevistas, observación estructurada, diarios, encuestas, intercept y mystery shopping (campo físico), analítica de comportamiento. Análisis: diseño muestral, codificación, triangulación de métodos y fuentes, síntesis.
-T5 MARCO · Frameworks de ciencias del comportamiento para leer conducta (COM-B, EAST); systems thinking.
-T6 ARTEFACTO · Insight; plan y estrategia de investigación.
-T7 CALIDAD Y ÉTICA · Calidad y suficiencia de la evidencia; gestión de sesgos; límites de validez; consentimiento y privacidad.
-T9 COMPETENCIA · Pensamiento crítico.</t>
+          <t>META-CAPACIDAD: Estrategia de investigación: componer objetivo, enfoque, metodología y técnicas de forma coherente con la decisión que se necesita tomar.
+OBJETIVO: Problem framing (de decisión de negocio a pregunta de investigación y conducta objetivo); exploración de necesidades, experiencias y contexto; diagnóstico conductual; diagnóstico sistémico.
+ENFOQUE: Cualitativo, cuantitativo y mixto; evidencia primaria y secundaria.
+METODOLOGÍA: Desk research (evidencia secundaria); investigación en campo / etnográfica; estudios longitudinales y de seguimiento.
+TÉCNICA: Recolección: entrevistas, observación estructurada, diarios, encuestas, intercept y mystery shopping (campo físico), analítica de comportamiento. Análisis: diseño muestral, codificación, triangulación de métodos y fuentes, síntesis.
+MARCO: Frameworks de ciencias del comportamiento para leer conducta (COM-B, EAST); systems thinking.
+ARTEFACTO: Insight; plan y estrategia de investigación.
+CALIDAD Y ÉTICA: Calidad y suficiencia de la evidencia; gestión de sesgos; límites de validez; consentimiento y privacidad.
+COMPETENCIAS: Pensamiento crítico.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -5076,13 +5084,15 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
-T1 OBJETIVO · Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas.
-T5 MARCO · Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio.
-T4 TÉCNICA (análisis y decisión) · Síntesis estratégica; evaluación de valor, viabilidad, riesgo y esfuerzo; matrices de priorización; exploración de escenarios y trade-offs.
-T6 ARTEFACTO · Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica.
-T7 CALIDAD Y ÉTICA · Supuestos explícitos; estándar de evidencia exigible según el tipo de decisión; ética de la intervención.
-T9 COMPETENCIA · Pensamiento crítico; business acumen; storytelling estratégico.</t>
+          <t>META-CAPACIDAD: Juicio estratégico: decidir qué problema merece resolverse y con cuánta evidencia basta para decidirlo, haciendo explícito el riesgo de equivocarse.
+OBJETIVO: Problem reframing; opportunity framing; formulación y priorización de hipótesis estratégicas; definición de direcciones y de trade-offs.
+ENFOQUE: Integración de la evidencia de usuario, de comportamiento y de negocio; lectura divergente para abrir alternativas y convergente para cerrar la decisión; evidencia primaria, secundaria y de mercado.
+METODOLOGÍA: Síntesis estratégica sobre evidencia acumulada; análisis del espacio de problema y de oportunidades; análisis de escenarios; modelado de sistemas y de actores.
+TÉCNICA: Encuadre: árboles de problema, reformulación de la pregunta, mapas de oportunidad. Decisión: matrices de priorización, evaluación de valor, viabilidad, riesgo y esfuerzo, análisis de trade-offs, pre-mortem.
+MARCO: Frameworks de Research, Design y Behavioral Science (COM-B, EAST, MINDSPACE); systems thinking; teoría del cambio; modelos de negocio y de valor.
+ARTEFACTO: Problema reencuadrado; mapa de oportunidades; hipótesis priorizadas; narrativa estratégica de la decisión.
+CALIDAD Y ÉTICA: Supuestos explícitos y trazables; estándar de evidencia exigible según el tipo de decisión; declaración del riesgo de equivocarse; ética de la intervención propuesta.
+COMPETENCIAS: Pensamiento crítico; business acumen; storytelling estratégico.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -5142,15 +5152,15 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>E3 ESPECIALIDAD · Diseño conductual (única especialidad de diseño evaluada por esta matriz).
-T0 META-CAPACIDAD · Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
-T1 OBJETIVO · Traducir evidencia y estrategia en principios, conceptos e intervenciones; intervenir sobre una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
-T5 MARCO · Arquitectura de decisiones; journey thinking; systems thinking.
-T5b PALANCAS DE INTERVENCIÓN · Fricción y esfuerzo; defaults; timing y saliencia; framing y comunicación conductual; incentivos; normas sociales; personalización.
-T4 TÉCNICA · Ideación y conceptualización; traducción de insights a criterios de diseño; prototipado conceptual; behavioral walkthrough; diseño de contenido conductual.
-T6 ARTEFACTO · Principios y criterios de diseño; concepto de intervención; blueprint de orquestación.
-T7 CALIDAD Y ÉTICA · Ética de la influencia (transparencia, autonomía de la persona, no explotación de sesgos); testeabilidad de la intervención.
-X MODELO DE COLABORACIÓN (no es capacidad; describe alcance) · Acompañamiento a Product y Service Design en la conceptualización y orquestación de la experiencia.</t>
+          <t>META-CAPACIDAD: Criterio de intervención: decidir cuánta intervención pide una conducta, elegir la palanca proporcional al problema y al riesgo ético, y reconocer cuándo lo correcto es no intervenir.
+OBJETIVO: Traducir evidencia y estrategia en principios, conceptos e intervenciones; modificar una conducta objetivo; orquestar la experiencia a través de touchpoints y canales.
+ENFOQUE: Diseño conductual, única especialidad de diseño de la matriz. Se diseña sobre conducta observada y no sobre conducta declarada; intervención puntual frente a sistema de intervenciones; reducir fricción frente a añadir refuerzo.
+METODOLOGÍA: Diseño de intervenciones conductuales; arquitectura de decisiones aplicada a un journey; ciclos iterativos de concepto, prueba y ajuste; co-diseño con las áreas dueñas de la experiencia.
+TÉCNICA: Palancas: fricción y esfuerzo, defaults, timing y saliencia, framing y comunicación conductual, incentivos, normas sociales, personalización. Proceso: traducción de insights a criterios de diseño, ideación y conceptualización, prototipado conceptual, behavioral walkthrough, diseño de contenido conductual.
+MARCO: Arquitectura de decisiones; journey thinking; systems thinking; taxonomías de palancas y de sesgos.
+ARTEFACTO: Principios y criterios de diseño; concepto de intervención; prototipo conceptual; blueprint de orquestación; hipótesis conductual lista para validar.
+CALIDAD Y ÉTICA: Ética de la influencia — transparencia, autonomía de la persona, no explotación de sesgos, reversibilidad de la intervención; proporcionalidad entre el problema y la palanca; testeabilidad; equidad del efecto entre segmentos.
+COMPETENCIAS: Pensamiento crítico aplicado al propio diseño; comunicación visual y narrativa del concepto; escucha y traducción entre disciplinas.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5210,14 +5220,15 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
-T1 OBJETIVO · UX validation (concepto, prototipo, experiencia); evaluación del efecto de intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
-T2 ENFOQUE · Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto.
-T3 METODOLOGÍA · Diseño experimental; RCT; cuasi-experimentos; pre-post con grupo de control; pruebas de concepto y prototipo; piloto en campo (físico) y en producto (digital).
-T4 TÉCNICA · Formulación operacional de hipótesis y variables; A/B testing y multivariante; concept &amp; prototype testing; usability testing; analytics e instrumentación; análisis estadístico.
-T5 MARCO · Inferencia causal; teoría del cambio; jerarquía de evidencia.
-T6 ARTEFACTO · Hipótesis operacionalizada; métricas y criterios de éxito; lectura de resultados y recomendación de decisión.
-T7 CALIDAD Y ÉTICA · Validez interna y externa; control de variables; potencia y tamaño muestral; triangulación como criterio de robustez; ética experimental (consentimiento, grupos de control, reversibilidad).</t>
+          <t>META-CAPACIDAD: Criterio de evidencia: decidir cuánto rigor exige cada decisión y cuánto sería desperdiciarlo, ajustando el diseño al costo, al riesgo y a la reversibilidad.
+OBJETIVO: UX validation (concepto, prototipo, experiencia); evaluación del efecto de las intervenciones conductuales; evaluación de impacto; decisión de iterar, escalar o detener.
+ENFOQUE: Observacional frente a experimental; cuantitativo, cualitativo de validación y mixto; medición en condiciones controladas frente a medición en condiciones reales.
+METODOLOGÍA: Diseño experimental; RCT; cuasi-experimentos por sede, territorio o cohorte; pre-post con grupo de control; pruebas de concepto y de prototipo; piloto en campo (físico) y en producto (digital).
+TÉCNICA: Diseño: operacionalización de hipótesis y variables, definición de grupos y regla de asignación, cálculo de tamaño muestral. Ejecución y análisis: A/B testing y multivariante, concept &amp; prototype testing, usability testing, analytics e instrumentación, análisis estadístico y por segmentos.
+MARCO: Inferencia causal; teoría del cambio; jerarquía de evidencia; modelo lógico de la intervención (el mecanismo por el que se espera que funcione).
+ARTEFACTO: Hipótesis operacionalizada; métricas y criterios de éxito definidos antes de medir; lectura de resultados con tamaño de efecto; recomendación de decisión.
+CALIDAD Y ÉTICA: Validez interna y externa; control de variables; potencia y tamaño muestral; triangulación como criterio de robustez; ética experimental — consentimiento, uso de grupos de control, reversibilidad y no daño al grupo no expuesto.
+COMPETENCIAS: Honestidad intelectual ante resultados negativos; comunicación de la incertidumbre; rigor en la lectura de datos ajenos.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -5277,13 +5288,15 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>T0 META-CAPACIDAD · Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
-T1 OBJETIVO · Escalar conocimiento, prácticas y capacidades; sostener la decisión basada en evidencia.
-T8 PRÁCTICA OPERATIVA · ResearchOps; BehavioralOps; KnowledgeOps; gestión y activación del conocimiento; repositorios y trazabilidad; automatización; capability building; mejora continua.
-T7 GOBERNANZA, CALIDAD Y ÉTICA · Estándares metodológicos; gobernanza de datos y privacidad; gestión de calidad; ética aplicada.
-T7b ÉTICA DEL LIDERAZGO · Se mide en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico — sin acoso, sin mansplaining, sin conductas excluyentes. El umbral no entra en la ponderación: su incumplimiento verificado bloquea el nivel. Ver hoja «4. Ética del liderazgo».
-T6 ARTEFACTO · Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council.
-T9 COMPETENCIA · Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
+          <t>META-CAPACIDAD: Criterio de escalamiento y liderazgo: decidir qué se estandariza, qué se deja variar y a qué ritmo se le puede exigir a un equipo, sosteniendo el equilibrio entre lo que el equipo produce y lo que el equipo puede sostener.
+OBJETIVO: Escalar conocimiento, prácticas y capacidades; desarrollar personas; sostener una cultura de decisión basada en evidencia.
+ENFOQUE: Evidencia acumulativa frente a estudio aislado; estandarizar frente a dejar variar; construir capacidad interna frente a resolver por encargo.
+METODOLOGÍA: ResearchOps, BehavioralOps y KnowledgeOps como sistemas de trabajo; gobernanza de estándares y de datos; capability building y modelos de desarrollo de personas; mejora continua.
+TÉCNICA: Conocimiento: repositorios y taxonomías de evidencia, activación y democratización del conocimiento, automatización de tareas operativas, trazabilidad. Liderazgo y equipo: feedback ascendente anónimo, observación estructurada de reuniones (habla, interrupciones y atribución de ideas), registro de asignación de oportunidades visibles, planes de desarrollo, entrevista de salida.
+MARCO: Systems thinking aplicado a la propia capacidad; modelo de madurez de la práctica; ciclo de mejora continua; el propio marco conductual aplicado al equipo — la conducta de quien lidera también es conducta observable.
+ARTEFACTO: Estándares y playbooks; repositorio de evidencia; catálogo de intervenciones reutilizables; modelo de capacidades del Council; tablero del equilibrio productividad–satisfacción del equipo.
+CALIDAD Y ÉTICA: Estándares metodológicos; gobernanza de datos, privacidad y trazabilidad; gestión de calidad. Ética del liderazgo, en dos partes que no se mezclan. EQUILIBRIO (se pondera): productividad del equipo ↔ satisfacción del equipo con la persona que lidera, leídas en el mismo periodo y nunca por separado. UMBRAL (se verifica, no se pondera): respeto básico, sin acoso, sin mansplaining, sin conductas excluyentes; su incumplimiento verificado bloquea el nivel y no entra en la ponderación.
+COMPETENCIAS: Stakeholder management; influencia; comunicación estratégica; facilitación; mentoring; priorización de portafolio.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">

--- a/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
+++ b/matriz-expertiz/Propuesta_Matriz_expertiz_taxonomias.xlsx
@@ -5062,7 +5062,14 @@
           <t>Define la estrategia de conocimiento e insights, conectando evidencia acumulativa para anticipar preguntas y orientar decisiones estratégicas.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="n"/>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>· Un plan de investigación con la justificación del método frente a las alternativas descartadas.
+· Un estudio completo con su guía, criterio muestral y notas de campo.
+· Un set de insights trazables a la evidencia que los sustenta (verbatims, datos, fuentes).
+· Un caso en que la evidencia cambió la decisión que ya se iba a tomar.</t>
+        </is>
+      </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
           <t>Buscar: amplía y acelera la búsqueda de evidencia interna y externa.
@@ -5130,7 +5137,14 @@
           <t>Construye marcos estratégicos que transforman cómo la organización comprende problemas y oportunidades, influyendo en prioridades y decisiones de negocio</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n"/>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>· Un problema reencuadrado: el enunciado inicial, el final y el razonamiento entre ambos.
+· Un mapa de oportunidades con los criterios de priorización explícitos.
+· Una decisión tomada con evidencia parcial, con el umbral de suficiencia declarado antes.
+· Una recomendación que se sostuvo ante negocio frente a objeciones.</t>
+        </is>
+      </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
           <t>Reencuadrar: propone diferentes formas de interpretar y formular un problema.
@@ -5198,7 +5212,14 @@
           <t>Define principios y modelos que transforman cómo RIMAC diseña decisiones, experiencias e intervenciones basadas en evidencia</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n"/>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>· Una intervención conductual documentada: conducta objetivo, palanca elegida y por qué esa.
+· Principios y criterios de diseño que otro equipo usó después.
+· Un blueprint de orquestación a través de canales.
+· Una intervención descartada por desproporcionada o por riesgo ético, con el razonamiento escrito.</t>
+        </is>
+      </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
           <t>Idear: genera alternativas de conceptos, experiencias e intervenciones.
@@ -5266,7 +5287,14 @@
           <t>Define estándares y sistemas de experimentación y evidencia acumulativa que orientan decisiones estratégicas, escalamiento e inversión.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n"/>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>· Un diseño experimental completo: hipótesis, variables, regla de asignación y tamaño muestral.
+· Una lectura de resultados con tamaño de efecto y límites de validez declarados.
+· Dos decisiones resueltas con distinto nivel de rigor, con la justificación de cada una.
+· Un caso de resultado negativo en que se detuvo o se rehízo la intervención.</t>
+        </is>
+      </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
           <t>Formular: ayuda a convertir supuestos en hipótesis, variables y criterios de éxito.
@@ -5334,7 +5362,14 @@
           <t>Define la gobernanza y evolución de Customer Science, construyendo una capacidad organizacional ética, reconocida, acumulativa y escalable</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n"/>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>· Un estándar o playbook adoptado por otros sin imposición.
+· Evidencia reutilizada por alguien que no participó del estudio original.
+· El indicador de entrega del equipo y su feedback ascendente del mismo periodo, leídos juntos.
+· Un plan de desarrollo con progresión demostrable de otra persona.</t>
+        </is>
+      </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
           <t>Automatizar: reduce tareas operativas y repetitivas de ResearchOps y BehavioralOps.
